--- a/zy72118/data/BATCH-2026-002_experiment.xlsx
+++ b/zy72118/data/BATCH-2026-002_experiment.xlsx
@@ -501,7 +501,7 @@
         <v>103.333</v>
       </c>
       <c r="D6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -515,7 +515,7 @@
         <v>116.667</v>
       </c>
       <c r="D7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -651,7 +651,7 @@
         <v>223.333</v>
       </c>
       <c r="D15" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -668,7 +668,7 @@
         <v>236.667</v>
       </c>
       <c r="D16" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -685,7 +685,7 @@
         <v>250</v>
       </c>
       <c r="D17" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -702,7 +702,7 @@
         <v>263.333</v>
       </c>
       <c r="D18" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -719,7 +719,7 @@
         <v>276.667</v>
       </c>
       <c r="D19" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -736,7 +736,7 @@
         <v>290</v>
       </c>
       <c r="D20" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -753,7 +753,7 @@
         <v>303.333</v>
       </c>
       <c r="D21" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -787,7 +787,7 @@
         <v>330</v>
       </c>
       <c r="D23" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
@@ -804,7 +804,7 @@
         <v>343.333</v>
       </c>
       <c r="D24" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
@@ -821,7 +821,7 @@
         <v>356.667</v>
       </c>
       <c r="D25" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
@@ -838,7 +838,7 @@
         <v>370</v>
       </c>
       <c r="D26" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
@@ -855,7 +855,7 @@
         <v>383.333</v>
       </c>
       <c r="D27" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
@@ -872,7 +872,7 @@
         <v>396.667</v>
       </c>
       <c r="D28" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>410</v>
       </c>
       <c r="D29" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E29" t="s">
         <v>8</v>
@@ -906,7 +906,7 @@
         <v>423.333</v>
       </c>
       <c r="D30" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E30" t="s">
         <v>8</v>
@@ -923,7 +923,7 @@
         <v>436.667</v>
       </c>
       <c r="D31" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E31" t="s">
         <v>8</v>
@@ -940,7 +940,7 @@
         <v>450</v>
       </c>
       <c r="D32" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E32" t="s">
         <v>8</v>
